--- a/Distribucion/Excels/VIESGO.xlsx
+++ b/Distribucion/Excels/VIESGO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:H97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,6 +464,11 @@
           <t>Latitud</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Comunidad</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -493,6 +498,11 @@
       <c r="G2" t="n">
         <v>43.27075900397912</v>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -522,6 +532,11 @@
       <c r="G3" t="n">
         <v>43.24279239156314</v>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,6 +566,11 @@
       <c r="G4" t="n">
         <v>43.53122801606191</v>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -580,6 +600,11 @@
       <c r="G5" t="n">
         <v>43.47880622659991</v>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -609,6 +634,11 @@
       <c r="G6" t="n">
         <v>43.3892359303755</v>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -638,6 +668,11 @@
       <c r="G7" t="n">
         <v>43.53853334835589</v>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -667,6 +702,11 @@
       <c r="G8" t="n">
         <v>43.38945666170413</v>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -696,6 +736,11 @@
       <c r="G9" t="n">
         <v>43.46203510820568</v>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -725,6 +770,11 @@
       <c r="G10" t="n">
         <v>43.4232082919763</v>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -754,6 +804,11 @@
       <c r="G11" t="n">
         <v>43.56122570485174</v>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -783,6 +838,11 @@
       <c r="G12" t="n">
         <v>43.30084190800687</v>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -812,6 +872,11 @@
       <c r="G13" t="n">
         <v>43.26008664943944</v>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -841,6 +906,11 @@
       <c r="G14" t="n">
         <v>43.13945882442995</v>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -870,6 +940,11 @@
       <c r="G15" t="n">
         <v>43.27136476483958</v>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -899,6 +974,11 @@
       <c r="G16" t="n">
         <v>43.16640274651714</v>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -928,6 +1008,11 @@
       <c r="G17" t="n">
         <v>43.14511935644313</v>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -957,6 +1042,11 @@
       <c r="G18" t="n">
         <v>43.23614670268638</v>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -986,6 +1076,11 @@
       <c r="G19" t="n">
         <v>43.37955873191738</v>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1015,6 +1110,11 @@
       <c r="G20" t="n">
         <v>43.19777685285425</v>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1044,6 +1144,11 @@
       <c r="G21" t="n">
         <v>43.2747567872949</v>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1073,6 +1178,11 @@
       <c r="G22" t="n">
         <v>43.2746883687341</v>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1102,6 +1212,11 @@
       <c r="G23" t="n">
         <v>43.10472745811583</v>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1131,6 +1246,11 @@
       <c r="G24" t="n">
         <v>43.02685885981288</v>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Principado de Asturias</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1160,6 +1280,11 @@
       <c r="G25" t="n">
         <v>43.39608674528703</v>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1189,6 +1314,11 @@
       <c r="G26" t="n">
         <v>43.24237918692837</v>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1218,6 +1348,11 @@
       <c r="G27" t="n">
         <v>43.39107016771121</v>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1247,6 +1382,11 @@
       <c r="G28" t="n">
         <v>43.41433202199211</v>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1276,6 +1416,11 @@
       <c r="G29" t="n">
         <v>43.39800586750414</v>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1305,6 +1450,11 @@
       <c r="G30" t="n">
         <v>43.3471632317849</v>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1334,6 +1484,11 @@
       <c r="G31" t="n">
         <v>43.35937326950445</v>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1363,6 +1518,11 @@
       <c r="G32" t="n">
         <v>43.21284646572629</v>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1392,6 +1552,11 @@
       <c r="G33" t="n">
         <v>43.43589570137751</v>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1421,6 +1586,11 @@
       <c r="G34" t="n">
         <v>43.45088323570684</v>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1450,6 +1620,11 @@
       <c r="G35" t="n">
         <v>43.46301378591188</v>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1479,6 +1654,11 @@
       <c r="G36" t="n">
         <v>43.44057763739843</v>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1508,6 +1688,11 @@
       <c r="G37" t="n">
         <v>43.40532025206969</v>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1537,6 +1722,11 @@
       <c r="G38" t="n">
         <v>43.47508817557549</v>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1566,6 +1756,11 @@
       <c r="G39" t="n">
         <v>43.43738320266608</v>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1595,6 +1790,11 @@
       <c r="G40" t="n">
         <v>43.45008634760416</v>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1624,6 +1824,11 @@
       <c r="G41" t="n">
         <v>43.4645308708133</v>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1653,6 +1858,11 @@
       <c r="G42" t="n">
         <v>43.45452367107463</v>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1682,6 +1892,11 @@
       <c r="G43" t="n">
         <v>43.42321622158387</v>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1711,6 +1926,11 @@
       <c r="G44" t="n">
         <v>43.4492602961403</v>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1740,6 +1960,11 @@
       <c r="G45" t="n">
         <v>43.39274198821905</v>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1769,6 +1994,11 @@
       <c r="G46" t="n">
         <v>43.47136753918428</v>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1798,6 +2028,11 @@
       <c r="G47" t="n">
         <v>43.43102969181349</v>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1827,6 +2062,11 @@
       <c r="G48" t="n">
         <v>43.26160559488196</v>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1856,6 +2096,11 @@
       <c r="G49" t="n">
         <v>43.39613254149651</v>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1885,6 +2130,11 @@
       <c r="G50" t="n">
         <v>43.32343479663642</v>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1914,6 +2164,11 @@
       <c r="G51" t="n">
         <v>43.03519040770468</v>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1943,6 +2198,11 @@
       <c r="G52" t="n">
         <v>42.87934767695143</v>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1972,6 +2232,11 @@
       <c r="G53" t="n">
         <v>42.80456078330076</v>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2001,6 +2266,11 @@
       <c r="G54" t="n">
         <v>42.98813071974366</v>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2030,6 +2300,11 @@
       <c r="G55" t="n">
         <v>42.87501573297278</v>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2059,6 +2334,11 @@
       <c r="G56" t="n">
         <v>43.17414439119321</v>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2088,6 +2368,11 @@
       <c r="G57" t="n">
         <v>43.31215822233923</v>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2117,6 +2402,11 @@
       <c r="G58" t="n">
         <v>43.28039035897601</v>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2146,6 +2436,11 @@
       <c r="G59" t="n">
         <v>43.36906247104279</v>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2175,6 +2470,11 @@
       <c r="G60" t="n">
         <v>43.25209420114358</v>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2204,6 +2504,11 @@
       <c r="G61" t="n">
         <v>43.32964895046565</v>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2233,6 +2538,11 @@
       <c r="G62" t="n">
         <v>43.25230326855753</v>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2262,6 +2572,11 @@
       <c r="G63" t="n">
         <v>43.32346801115301</v>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2291,6 +2606,11 @@
       <c r="G64" t="n">
         <v>43.25627742139321</v>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2320,6 +2640,11 @@
       <c r="G65" t="n">
         <v>43.16483371940252</v>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2349,6 +2674,11 @@
       <c r="G66" t="n">
         <v>43.35740511022636</v>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2378,6 +2708,11 @@
       <c r="G67" t="n">
         <v>43.14929785073039</v>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2407,6 +2742,11 @@
       <c r="G68" t="n">
         <v>43.33557836808084</v>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2436,6 +2776,11 @@
       <c r="G69" t="n">
         <v>43.36812549169798</v>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2465,6 +2810,11 @@
       <c r="G70" t="n">
         <v>43.22266808411101</v>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2494,6 +2844,11 @@
       <c r="G71" t="n">
         <v>43.35888911795318</v>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2523,6 +2878,11 @@
       <c r="G72" t="n">
         <v>43.37570336113989</v>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2552,6 +2912,11 @@
       <c r="G73" t="n">
         <v>43.32795103515409</v>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2581,6 +2946,11 @@
       <c r="G74" t="n">
         <v>43.1195090771279</v>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2610,6 +2980,11 @@
       <c r="G75" t="n">
         <v>43.26637216893302</v>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Cantabria</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2639,6 +3014,11 @@
       <c r="G76" t="n">
         <v>41.10852506665827</v>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Provincia no encontrada</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2668,6 +3048,11 @@
       <c r="G77" t="n">
         <v>42.98828200087193</v>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2697,6 +3082,11 @@
       <c r="G78" t="n">
         <v>42.40286921604282</v>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2726,6 +3116,11 @@
       <c r="G79" t="n">
         <v>42.51011537559259</v>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2755,6 +3150,11 @@
       <c r="G80" t="n">
         <v>42.79481027505688</v>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2784,6 +3184,11 @@
       <c r="G81" t="n">
         <v>42.78367272371662</v>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2813,6 +3218,11 @@
       <c r="G82" t="n">
         <v>42.90374986152523</v>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2842,6 +3252,11 @@
       <c r="G83" t="n">
         <v>42.34555422095354</v>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2871,6 +3286,11 @@
       <c r="G84" t="n">
         <v>42.85491203230819</v>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2900,6 +3320,11 @@
       <c r="G85" t="n">
         <v>42.5993896286173</v>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2929,6 +3354,11 @@
       <c r="G86" t="n">
         <v>42.78587818679645</v>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2958,6 +3388,11 @@
       <c r="G87" t="n">
         <v>42.40988003938657</v>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2987,6 +3422,11 @@
       <c r="G88" t="n">
         <v>42.62500859183022</v>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Castilla y León</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3016,6 +3456,11 @@
       <c r="G89" t="n">
         <v>43.58905101568634</v>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3045,6 +3490,11 @@
       <c r="G90" t="n">
         <v>43.42871019711748</v>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3074,6 +3524,11 @@
       <c r="G91" t="n">
         <v>43.08400997768577</v>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3103,6 +3558,11 @@
       <c r="G92" t="n">
         <v>43.12849849953469</v>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3132,6 +3592,11 @@
       <c r="G93" t="n">
         <v>43.43183187632081</v>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3161,6 +3626,11 @@
       <c r="G94" t="n">
         <v>43.01701303179894</v>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3190,6 +3660,11 @@
       <c r="G95" t="n">
         <v>43.42490520050706</v>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3219,6 +3694,11 @@
       <c r="G96" t="n">
         <v>43.31395233174032</v>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3247,6 +3727,11 @@
       </c>
       <c r="G97" t="n">
         <v>43.53534152173235</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Galicia</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Distribucion/Excels/VIESGO.xlsx
+++ b/Distribucion/Excels/VIESGO.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EL PALO 400 kV</t>
+          <t>EL PALO 400</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PESOZ 400 kV</t>
+          <t>PESOZ 400</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SALAS 400 kV</t>
+          <t>SALAS 400</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SALAS 400 kV</t>
+          <t>SALAS 400</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SALAS 400 kV</t>
+          <t>SALAS 400</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SALAS 400 kV</t>
+          <t>SALAS 400</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SALAS 400 kV</t>
+          <t>SALAS 400</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SALAS 400 kV</t>
+          <t>SALAS 400</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SALAS 400 kV</t>
+          <t>SALAS 400</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SALAS 400 kV</t>
+          <t>SALAS 400</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SIERO 220 kV</t>
+          <t>SIERO 220</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SIERO 220 kV</t>
+          <t>SIERO 220</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SIERO 220 kV</t>
+          <t>SIERO 220</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SIERO 220 kV</t>
+          <t>SIERO 220</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SIERO 220 kV</t>
+          <t>SIERO 220</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SIERO 220 kV</t>
+          <t>SIERO 220</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SIERO 220 kV</t>
+          <t>SIERO 220</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SIERO 220 kV</t>
+          <t>SIERO 220</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SIERO 220 kV</t>
+          <t>SIERO 220</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SOTO 220 kV</t>
+          <t>SOTO 220</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SOTO 220 kV</t>
+          <t>SOTO 220</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>TELLEDO 220 kV</t>
+          <t>TELLEDO 220</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>TELLEDO 220 kV</t>
+          <t>TELLEDO 220</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ASTILLERO 220 kV</t>
+          <t>ASTILLERO 220</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ASTILLERO 220 kV</t>
+          <t>ASTILLERO 220</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ASTILLERO 220 kV</t>
+          <t>ASTILLERO 220</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ASTILLERO 220 kV</t>
+          <t>ASTILLERO 220</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ASTILLERO 220 kV</t>
+          <t>ASTILLERO 220</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ASTILLERO 220 kV</t>
+          <t>ASTILLERO 220</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ASTILLERO 220 kV</t>
+          <t>ASTILLERO 220</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ASTILLERO 220 kV</t>
+          <t>ASTILLERO 220</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CACICEDO 220 kV</t>
+          <t>CACICEDO 220</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CACICEDO 220 kV</t>
+          <t>CACICEDO 220</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CACICEDO 220 kV</t>
+          <t>CACICEDO 220</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CACICEDO 220 kV</t>
+          <t>CACICEDO 220</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CACICEDO 220 kV</t>
+          <t>CACICEDO 220</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CACICEDO 220 kV</t>
+          <t>CACICEDO 220</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CACICEDO 220 kV</t>
+          <t>CACICEDO 220</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CACICEDO 220 kV</t>
+          <t>CACICEDO 220</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CACICEDO 220 kV</t>
+          <t>CACICEDO 220</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>CACICEDO 220 kV</t>
+          <t>CACICEDO 220</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CICERO 220 kV</t>
+          <t>CICERO 220</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CICERO 220 kV</t>
+          <t>CICERO 220</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CICERO 220 kV</t>
+          <t>CICERO 220</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CICERO 220 kV</t>
+          <t>CICERO 220</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CICERO 220 kV</t>
+          <t>CICERO 220</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>CICERO 220 kV</t>
+          <t>CICERO 220</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CICERO 220 kV</t>
+          <t>CICERO 220</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CICERO 220 kV</t>
+          <t>CICERO 220</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Mataporquera 220 kV</t>
+          <t>MATAPORQUERA 220</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Mataporquera 220 kV</t>
+          <t>MATAPORQUERA 220</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Mataporquera 220 kV</t>
+          <t>MATAPORQUERA 220</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Mataporquera 220 kV</t>
+          <t>MATAPORQUERA 220</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Mataporquera 220 kV</t>
+          <t>MATAPORQUERA 220</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>P.S.M. 220 KV</t>
+          <t>P.S.M. 220</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>P.S.M. 220 KV</t>
+          <t>P.S.M. 220</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>P.S.M. 220 KV</t>
+          <t>P.S.M. 220</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>P.S.M. 220 KV</t>
+          <t>P.S.M. 220</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>P.S.M. 220 KV</t>
+          <t>P.S.M. 220</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>P.S.M. 220 KV</t>
+          <t>P.S.M. 220</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>P.S.M. 220 KV</t>
+          <t>P.S.M. 220</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>P.S.M. 220 KV</t>
+          <t>P.S.M. 220</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>P.S.M. 220 KV</t>
+          <t>P.S.M. 220</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>P.S.M. 220 KV</t>
+          <t>P.S.M. 220</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>P.S.M. 220 KV</t>
+          <t>P.S.M. 220</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>P.S.M. 220 KV</t>
+          <t>P.S.M. 220</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>P.S.M. 220 KV</t>
+          <t>P.S.M. 220</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>P.S.M. 220 KV</t>
+          <t>P.S.M. 220</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>P.S.M. 220 KV</t>
+          <t>P.S.M. 220</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>P.S.M. 220 KV</t>
+          <t>P.S.M. 220</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>P.S.M. 220 KV</t>
+          <t>P.S.M. 220</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>P.S.M. 220 KV</t>
+          <t>P.S.M. 220</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>P.S.M. 220 KV</t>
+          <t>P.S.M. 220</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>P.S.M. 220 KV</t>
+          <t>P.S.M. 220</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2989,7 +2989,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TARRAGON</t>
+          <t>TARRAGONA</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LA CANONJA 220 kV</t>
+          <t>LA CANONJA 220</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Provincia no encontrada</t>
+          <t>Cataluña</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Mataporquera 220 kV</t>
+          <t>MATAPORQUERA 220</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Mataporquera 220 kV</t>
+          <t>MATAPORQUERA 220</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Mataporquera 220 kV</t>
+          <t>MATAPORQUERA 220</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Mataporquera 220 kV</t>
+          <t>MATAPORQUERA 220</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Mataporquera 220 kV</t>
+          <t>MATAPORQUERA 220</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Mataporquera 220 kV</t>
+          <t>MATAPORQUERA 220</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Mataporquera 220 kV</t>
+          <t>MATAPORQUERA 220</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Mataporquera 220 kV</t>
+          <t>MATAPORQUERA 220</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Mataporquera 220 kV</t>
+          <t>MATAPORQUERA 220</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Mataporquera 220 kV</t>
+          <t>MATAPORQUERA 220</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Mataporquera 220 kV</t>
+          <t>MATAPORQUERA 220</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Mataporquera 220 kV</t>
+          <t>MATAPORQUERA 220</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>BOIMENTE 400 kV</t>
+          <t>BOIMENTE 400</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LUDRIO 400 kV</t>
+          <t>LUDRIO 400</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LUDRIO 400 kV</t>
+          <t>LUDRIO 400</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LUDRIO 400 kV</t>
+          <t>LUDRIO 400</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LUDRIO 400 kV</t>
+          <t>LUDRIO 400</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LUDRIO 400 kV</t>
+          <t>LUDRIO 400</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>P.G.R. 400 kV</t>
+          <t>P.G.R. 400</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>P.G.R. 400 kV</t>
+          <t>P.G.R. 400</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>SALAS 400 kV</t>
+          <t>SALAS 400</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
